--- a/신고신저가_20260813.xlsx
+++ b/신고신저가_20260813.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$K$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$N$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$N$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,23 +537,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -564,23 +564,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -591,23 +591,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -783,29 +783,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6345.53</v>
+        <v>6813.34</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.21</v>
+        <v>3.56</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8.210000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-15.12</v>
+        <v>-0.63</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-18.88</v>
+        <v>-13.14</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>50.58</v>
+        <v>61.68</v>
       </c>
       <c r="I4" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -821,29 +821,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>66970.22</v>
+        <v>68308.59</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.08</v>
+        <v>1.16</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>-1.14</v>
+        <v>3.03</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1.59</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6.74</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>33.04</v>
+        <v>35.7</v>
       </c>
       <c r="I5" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -859,29 +859,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3946.68</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.32</v>
+        <v>3926.96</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-0.5</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.76</v>
+        <v>0.68</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.72</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-5.53</v>
+        <v>-5.04</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="I6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -897,29 +897,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4690.92</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.58</v>
+        <v>4663.95</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-0.57</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.57</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-4.55</v>
+        <v>-4.03</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.32</v>
+        <v>0.73</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -935,29 +935,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25440.17</v>
+        <v>25373.97</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-1.84</v>
+        <v>-0.61</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.52</v>
+        <v>2.81</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-3.45</v>
+        <v>-3.84</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1</v>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -973,29 +973,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4776.44</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>-0.99</v>
+        <v>4781.79</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-3.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.07</v>
+        <v>0.87</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-5.8</v>
+        <v>-6.13</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-13.41</v>
+        <v>-13.31</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1909,20 +1909,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>20.1</v>
+        <v>15.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23">
@@ -1950,11 +1950,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1970,15 +1970,17 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>21.6</v>
+      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>25.2</v>
+        <v>29.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -1989,11 +1991,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -2011,13 +2013,13 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>21.2</v>
+        <v>25.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2028,35 +2030,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>26.4</v>
+      </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>25.7</v>
+        <v>34.4</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="26">
@@ -2067,11 +2071,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -2089,13 +2093,13 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>34.8</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -2106,11 +2110,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -2126,15 +2130,17 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>16.5</v>
+      </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
@@ -2145,11 +2151,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -2165,17 +2171,15 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>19.1</v>
+        <v>11.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
@@ -2186,11 +2190,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -2206,17 +2210,15 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>28.4</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="30">
@@ -2227,35 +2229,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>강세</t>
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>11.1</v>
+        <v>23.6</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2266,37 +2268,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>13.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="K31" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="32">
@@ -2307,35 +2307,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>13.2</v>
+      </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>12.4</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">
@@ -2346,11 +2348,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -2371,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>23.7</v>
+        <v>25.3</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="34">
@@ -2385,11 +2387,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2410,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>14.6</v>
+        <v>34.8</v>
       </c>
       <c r="K34" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="35">
@@ -2424,11 +2426,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -2444,17 +2446,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>34.1</v>
+        <v>18.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="36">
@@ -2504,11 +2504,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="K37" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="38">
@@ -2543,11 +2543,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>13.7</v>
+        <v>6.5</v>
       </c>
       <c r="K38" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="39">
@@ -2582,11 +2582,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>25.9</v>
+        <v>13.7</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="40">
@@ -2621,11 +2621,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2643,13 +2643,13 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>11.6</v>
+        <v>25.6</v>
       </c>
       <c r="K40" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41">
@@ -2660,35 +2660,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>32.4</v>
+      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>8.6</v>
+        <v>35.3</v>
       </c>
       <c r="K41" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="42">
@@ -2699,37 +2701,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>17</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>24</v>
+      </c>
+      <c r="I42" t="n">
         <v>13</v>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I42" t="n">
-        <v>6</v>
-      </c>
       <c r="J42" t="n">
-        <v>12.6</v>
+        <v>77.8</v>
       </c>
       <c r="K42" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="43">
@@ -2740,35 +2742,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>31.1</v>
+        <v>15.6</v>
       </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="44">
@@ -2779,35 +2781,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>3</v>
-      </c>
       <c r="J44" t="n">
-        <v>12</v>
+        <v>15.7</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2818,35 +2822,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>15.8</v>
+        <v>8.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="46">
@@ -2857,37 +2861,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I46" t="n">
         <v>6</v>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
-      </c>
       <c r="J46" t="n">
-        <v>15.7</v>
+        <v>12.4</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="47">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2908,25 +2912,25 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>12.7</v>
+        <v>3.7</v>
       </c>
       <c r="K47" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -2937,11 +2941,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2957,17 +2961,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>77.8</v>
+        <v>30.6</v>
       </c>
       <c r="K48" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="49">
@@ -2978,11 +2980,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -3000,13 +3002,13 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="K49" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="50">
@@ -3017,11 +3019,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -3037,17 +3039,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>11</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>7.9</v>
+        <v>12.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="51">
@@ -3058,11 +3058,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -3078,17 +3078,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>32.6</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>35.7</v>
+        <v>11.3</v>
       </c>
       <c r="K51" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="52">
@@ -3099,11 +3097,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -3119,15 +3117,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>10.8</v>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="53">
@@ -3159,16 +3159,16 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="I53" t="n">
         <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="K53" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="54">
@@ -3204,10 +3204,10 @@
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>24.8</v>
+        <v>23.8</v>
       </c>
       <c r="K54" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="55">
@@ -3239,16 +3239,16 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="I55" t="n">
         <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="K55" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="56">
@@ -3280,13 +3280,13 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I56" t="n">
         <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="K56" t="n">
         <v>1.7</v>
@@ -3327,10 +3327,10 @@
         <v>6</v>
       </c>
       <c r="J57" t="n">
-        <v>16.5</v>
+        <v>15.8</v>
       </c>
       <c r="K57" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="58">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="I58" t="n">
         <v>7</v>
       </c>
       <c r="J58" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="K58" t="n">
         <v>1.5</v>
@@ -3382,33 +3382,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>71</v>
+      </c>
+      <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>37.1</v>
+      </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="J59" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="K59" t="n">
-        <v>15.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="60">
@@ -3419,35 +3423,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>31.1</v>
+      </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>16.8</v>
+        <v>44.9</v>
       </c>
       <c r="K60" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="61">
@@ -3458,35 +3464,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>54.3</v>
+      </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
-        <v>15.5</v>
+        <v>52.2</v>
       </c>
       <c r="K61" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="62">
@@ -3497,11 +3505,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -3521,11 +3529,9 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>3.8</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="63">
@@ -3536,11 +3542,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3561,10 +3567,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>28.7</v>
+        <v>17</v>
       </c>
       <c r="K63" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="64">
@@ -3575,11 +3581,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3595,17 +3601,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>36.7</v>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
-        <v>81.8</v>
+        <v>15.1</v>
       </c>
       <c r="K64" t="n">
-        <v>10.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="65">
@@ -3616,11 +3620,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3638,13 +3642,13 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>15.1</v>
+        <v>19.2</v>
       </c>
       <c r="K65" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="66">
@@ -3655,11 +3659,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3675,17 +3679,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>6</v>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>6.5</v>
+        <v>27.9</v>
       </c>
       <c r="K66" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="67">
@@ -3696,11 +3698,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3718,13 +3720,13 @@
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>24.4</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="68">
@@ -3735,11 +3737,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3756,16 +3758,16 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>31.4</v>
+        <v>7.3</v>
       </c>
       <c r="I68" t="n">
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>45.4</v>
+        <v>6.7</v>
       </c>
       <c r="K68" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="69">
@@ -3776,11 +3778,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Health Services</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3798,13 +3800,13 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>7.3</v>
+        <v>24.1</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="70">
@@ -3815,11 +3817,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3837,13 +3839,13 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>19.9</v>
+        <v>7.2</v>
       </c>
       <c r="K70" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="71">
@@ -3854,11 +3856,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3874,15 +3876,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>11.4</v>
+      </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>27.2</v>
+        <v>19.1</v>
       </c>
       <c r="K71" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="72">
@@ -3893,11 +3897,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3913,17 +3917,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" t="n">
-        <v>31</v>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>38.3</v>
+        <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="73">
@@ -3934,11 +3936,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3954,13 +3956,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>30.8</v>
+      </c>
       <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="J73" t="n">
+        <v>39.7</v>
+      </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -3971,11 +3977,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3991,17 +3997,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" t="n">
-        <v>55.3</v>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" t="n">
-        <v>61</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -5032,19 +5034,19 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
@@ -5103,19 +5105,19 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-4.1</v>
+        <v>-2.4</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="I14" t="n">
         <v>9</v>
@@ -5174,19 +5176,19 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-6.9</v>
+        <v>-3.6</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -5245,19 +5247,19 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0.8</v>
-      </c>
       <c r="G16" s="6" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -5316,19 +5318,19 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>-0</v>
+        <v>-0.5</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
         <v>13</v>
@@ -5387,19 +5389,19 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-1.2</v>
+        <v>-2.3</v>
       </c>
       <c r="I18" t="n">
         <v>16</v>
@@ -5458,19 +5460,19 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-19.1</v>
+        <v>-11.9</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -5529,19 +5531,19 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-1</v>
+        <v>2.8</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-5.4</v>
+        <v>-0.6</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>21.8</v>
+        <v>24.2</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
@@ -5600,19 +5602,19 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-1.6</v>
+        <v>3.2</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>36.7</v>
+        <v>39.7</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
@@ -5671,19 +5673,19 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>16.9</v>
+        <v>19.9</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="I22" t="n">
         <v>10</v>
@@ -5742,19 +5744,19 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>-2</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I23" t="n">
         <v>15</v>
@@ -5813,19 +5815,19 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -5884,19 +5886,19 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-8.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="I25" t="n">
         <v>8</v>
@@ -5955,19 +5957,19 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
         <v>12</v>
@@ -6026,19 +6028,19 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>18.8</v>
+        <v>24.1</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>46.3</v>
+        <v>50.7</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -6097,19 +6099,19 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1.7</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
@@ -6168,19 +6170,19 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-4.4</v>
+        <v>-3.8</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-12.2</v>
+        <v>-7.6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-6.2</v>
+        <v>-5.8</v>
       </c>
       <c r="I29" t="n">
         <v>17</v>
@@ -6239,55 +6241,55 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>32.8</v>
+        <v>27.4</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>24.8</v>
+        <v>17.9</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-11.9</v>
+        <v>-13.7</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-14.4</v>
+        <v>-15.3</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>-13.5</v>
+        <v>-14.2</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>-1.2</v>
+        <v>-3.7</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -6310,55 +6312,55 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-4.1</v>
+        <v>-4.7</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-4.2</v>
+        <v>-5</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>26.2</v>
+        <v>22.9</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>32.1</v>
+        <v>27.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-12.8</v>
+        <v>-14.1</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-17.8</v>
+        <v>-18.6</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>-23.6</v>
+        <v>-23.2</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>-2</v>
+        <v>-4.1</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
@@ -6381,19 +6383,19 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-1.1</v>
+        <v>0.2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-3.3</v>
+        <v>-0.9</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-13.1</v>
+        <v>-12.9</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
@@ -6408,7 +6410,7 @@
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>-9.300000000000001</v>
@@ -6448,19 +6450,19 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1.7</v>
+        <v>-1.7</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-16.8</v>
+        <v>-13.1</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>48.6</v>
+        <v>46.2</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -6519,19 +6521,19 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1.8</v>
+        <v>-0.9</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-12.5</v>
+        <v>-10</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
@@ -6590,19 +6592,19 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-15.1</v>
+        <v>-12.4</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-7.5</v>
+        <v>-5.2</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
@@ -6661,19 +6663,19 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-17.6</v>
+        <v>-18.4</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>-10.2</v>
+        <v>-11.2</v>
       </c>
       <c r="I36" t="n">
         <v>9</v>
@@ -6728,19 +6730,19 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-18.5</v>
+        <v>-17.1</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-15.8</v>
+        <v>-16.4</v>
       </c>
       <c r="I37" t="n">
         <v>12</v>
@@ -6799,22 +6801,22 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-21.8</v>
+        <v>-22.1</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.3</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>27.1</v>
@@ -6866,22 +6868,22 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-4.3</v>
+        <v>-1.1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-16.8</v>
+        <v>-16</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>-13</v>
@@ -6940,19 +6942,19 @@
         <v>0</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>-2.8</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>10.8</v>
@@ -7008,22 +7010,22 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.9</v>
+        <v>-3.6</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-8.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.7</v>
+        <v>-3</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41" s="6" t="n">
         <v>101.1</v>
@@ -7079,22 +7081,22 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4.2</v>
+        <v>-2.4</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-12.7</v>
+        <v>-13.5</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>-15.2</v>
+        <v>-17.3</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>2.5</v>
@@ -7153,19 +7155,19 @@
         <v>0.4</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-1.1</v>
+        <v>0.5</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-0.6</v>
+        <v>-2.6</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-9.4</v>
+        <v>-9.1</v>
       </c>
       <c r="I43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>3.5</v>
@@ -7221,19 +7223,19 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>9.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
@@ -7292,19 +7294,19 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>8.1</v>
+        <v>3.7</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-5.1</v>
+        <v>-4</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-13.9</v>
+        <v>-14.2</v>
       </c>
       <c r="I45" t="n">
         <v>10</v>
@@ -7357,9 +7359,9 @@
   <conditionalFormatting sqref="D2:D45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-1.2"/>
+        <cfvo type="num" val="-3.6"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="4.2"/>
+        <cfvo type="num" val="3"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7369,9 +7371,9 @@
   <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-3.3"/>
+        <cfvo type="num" val="-2.5"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="9.9"/>
+        <cfvo type="num" val="6.5"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7381,9 +7383,9 @@
   <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-16.8"/>
+        <cfvo type="num" val="-13.1"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="12.6"/>
+        <cfvo type="num" val="9.300000000000001"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7393,9 +7395,9 @@
   <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-21.8"/>
+        <cfvo type="num" val="-22.1"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="18.8"/>
+        <cfvo type="num" val="24.1"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7405,9 +7407,9 @@
   <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="num" val="-16.8"/>
+        <cfvo type="num" val="-17.3"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="53.4"/>
+        <cfvo type="num" val="53.8"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -8871,7 +8873,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="J25" t="n">
         <v>14.4</v>
@@ -9940,7 +9942,7 @@
         <v>1.3</v>
       </c>
       <c r="H45" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="I45" t="n">
         <v>44.4</v>
@@ -11397,7 +11399,7 @@
         <v>13.1</v>
       </c>
       <c r="I72" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -11865,7 +11867,7 @@
         <v>10.5</v>
       </c>
       <c r="I81" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="J81" t="n">
         <v>22.6</v>
@@ -11947,7 +11949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12065,17 +12067,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5669</v>
+        <v>5702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.87</v>
+        <v>0.58</v>
       </c>
       <c r="H2" t="n">
-        <v>159.4</v>
+        <v>160.9</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
@@ -12094,43 +12096,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6098 JP Equity</t>
+          <t>6857 JP Equity</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Recruit Holdings Co., Ltd.</t>
+          <t>Advantest Corp.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16660</v>
+        <v>35940</v>
       </c>
       <c r="G3" t="n">
-        <v>3.06</v>
+        <v>4.02</v>
       </c>
       <c r="H3" t="n">
-        <v>137.7</v>
+        <v>151.2</v>
       </c>
       <c r="I3" t="n">
-        <v>32.1</v>
+        <v>39.9</v>
       </c>
       <c r="J3" t="n">
-        <v>40.7</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>13.1</v>
+        <v>25</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -12142,11 +12144,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
-        </is>
-      </c>
+      <c r="N3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -12154,51 +12152,59 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8001 JP Equity</t>
+          <t>6098 JP Equity</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Itochu Corporation</t>
+          <t>Recruit Holdings Co., Ltd.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2096</v>
+        <v>16790</v>
       </c>
       <c r="G4" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="H4" t="n">
-        <v>102</v>
+        <v>141.9</v>
       </c>
       <c r="I4" t="n">
-        <v>15.1</v>
+        <v>32.3</v>
       </c>
       <c r="J4" t="n">
-        <v>16.1</v>
+        <v>41.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>13.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>(전일) 리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -12206,43 +12212,41 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7974 JP Equity</t>
+          <t>7011 JP Equity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nintendo Co., Ltd.</t>
+          <t>Mitsubishi Heavy Industries, Ltd.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8488</v>
+        <v>4256</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>3.96</v>
       </c>
       <c r="H5" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>27.4</v>
-      </c>
+        <v>86.3</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>20.7</v>
+        <v>35.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -12250,16 +12254,12 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 닌텐도(게임기·소프트, 스위치): 1Q 매출 9.5%↓에도 영업이익 150%↑ 서프라이즈로 강세 지속</t>
-        </is>
-      </c>
+      <c r="N5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>신저가</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8802 JP Equity</t>
+          <t>8308 JP Equity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mitsubishi Estate Company, Limited</t>
+          <t>Resona Holdings, Inc.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -12283,27 +12283,33 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3684</v>
+        <v>2446.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.89</v>
+        <v>4.37</v>
       </c>
       <c r="H6" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>33.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.4</v>
+      </c>
       <c r="J6" t="n">
-        <v>15.7</v>
+        <v>20.6</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -12312,53 +12318,55 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4543 JP Equity</t>
+          <t>8309 JP Equity</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Terumo Corporation</t>
+          <t>Sumitomo Mitsui Trust Group, Inc.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2598.5</v>
+        <v>1753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.89</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>29.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>13.4</v>
+      </c>
       <c r="J7" t="n">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -12373,34 +12381,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7832 JP Equity</t>
+          <t>4543 JP Equity</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bandai Namco Holdings Inc.</t>
+          <t>Terumo Corporation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5362</v>
+        <v>2620.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.23</v>
+        <v>0.85</v>
       </c>
       <c r="H8" t="n">
-        <v>21.9</v>
+        <v>24.1</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -12410,7 +12418,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>(전일) 반다이남코(게임·완구 IP): 1분기 사상 최대 실적, 2분기 누계 가이던스도 상향</t>
+          <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
@@ -12441,13 +12449,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>499.7</v>
+        <v>499.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.33</v>
+        <v>-0.04</v>
       </c>
       <c r="H9" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
@@ -12474,107 +12482,107 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9104 JP Equity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mitsui O.S.K.Lines,Ltd.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6279</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7453 JP Equity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ryohin Keikaku Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Consumer Non-Durables</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>4495</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="H10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1812 JP Equity</t>
+          <t>8331 JP Equity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kajima Corporation</t>
+          <t>Chiba Bank, Ltd.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4868</v>
+        <v>2842</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="H11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16.5</v>
+      </c>
       <c r="J11" t="n">
-        <v>12.5</v>
+        <v>19.4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 카지마(종합건설): 특별한 뉴스 없음, 건설 섹터 동반 조정 추정</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -12582,53 +12590,55 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7733 JP Equity</t>
+          <t>5831 JP Equity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Olympus Corp.</t>
+          <t>Shizuoka Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2075.5</v>
+        <v>3480</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1</v>
+        <v>2.29</v>
       </c>
       <c r="H12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15.5</v>
+      </c>
       <c r="J12" t="n">
-        <v>29.2</v>
+        <v>18.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 올림푸스(내시경 등 의료기기): 1Q 매출 16.4%↑·영업이익 74.4%↑·순이익 2.1배로 예상 상회</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -12636,57 +12646,49 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7550 JP Equity</t>
+          <t>9435 JP Equity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zensho Holdings Co., Ltd.</t>
+          <t>Hikari Tsushin, Inc.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11340</v>
+        <v>40430</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2</v>
+        <v>1.46</v>
       </c>
       <c r="H13" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>33.5</v>
+        <v>11.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 젠쇼(스키야 등 외식체인): FY26.3 증수증익, 8/7 FY27.3 실적전망 상향 발표 후 상승 지속</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -12694,164 +12696,58 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OLD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9107 JP Equity</t>
+          <t>4188 JP Equity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kawasaki Kisen Kaisha, Ltd.</t>
+          <t>Mitsubishi Chemical Group Corporation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2871</v>
+        <v>1227</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.28</v>
+        <v>-1.56</v>
       </c>
       <c r="H14" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="I14" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="J14" t="n">
-        <v>14.3</v>
+        <v>33.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N14" s="7" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2801 JP Equity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Kikkoman Corporation</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Consumer Non-Durables</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1768.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4188 JP Equity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mitsubishi Chemical Group Corporation</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Process Industries</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1246.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N16"/>
+  <autoFilter ref="A1:N14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12862,7 +12758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12959,104 +12855,542 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2359 HK Equity</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WuXi AppTec Co., Ltd. Class H</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>203</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H2" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>(전일) 우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>992 HK Equity</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lenovo Group Limited</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Electronic Technology</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>(전일) 레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6951 HK Equity</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chaozhou Three-Circle (Group) Co., Ltd. Class H</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Electronic Technology</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>2 HK Equity</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CLP Holdings Limited</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="F5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K5" t="n">
         <v>1.8</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>27 HK Equity</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Galaxy Entertainment Group Limited</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19 HK Equity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Swire Pacific Limited Class A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Consumer Non-Durables</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1093 HK Equity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CSPC Pharmaceutical Group Limited</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1186 HK Equity</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>China Railway Construction Corporation Limited Class H</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Industrial Services</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3759 HK Equity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pharmaron Beijing Co., Ltd. Class H</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>(전일) 캉룽화청(신약 위탁연구 CRO): CXO 섹터 랠리 지속·실적 호조로 목표주가 상향 잇따름(개별 신규 촉매는 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>9866 HK Equity</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>NIO Inc. Class A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>35.68</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>16</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13067,7 +13401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13158,8 +13492,178 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>301165 CH Equity</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ruijie Networks Co., Ltd. Class A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Technology Services</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>603228 CH Equity</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Shenzhen Kinwong Electronic Co., Ltd. Class A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Electronic Technology</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>81</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>300759 CH Equity</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pharmaron Beijing Co., Ltd. Class A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Health Technology</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>(전일) 캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/신고신저가_20260813.xlsx
+++ b/신고신저가_20260813.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,56 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 지수는 미·일만 전진하고 중화권은 정체 — 그 안에서 금융(미·일)과 AI 하드웨어(레노버·어드반테스트·루이제)만 신고가를 만드는 좁고 선별적인 장세로 판단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/12): S&amp;P500 +0.26%(7,748·52주위치 99%)·나스닥 +0.54%, 신고70/신저11. 금융 순강도 +11(12MF 15.2배)·헬스테크 +10·비에너지소재 +9. 뉴몬트·애그니코 등 금광 7종 동반 신고가. XLK +1.5% 대 XLB -1.2%·XLY -1.1%. 브링커 +11.1%(FY26 4분기 서프라이즈), 텍사스퍼시픽랜드 -6.1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/13): 닛케이 +1.16%(68,309). 은행ETF +3.0%로 최강, 리소나 +4.4%·치바은행 +3.5%·스미토모미쓰이트러스트 +2.8% 일제 신고가 — 일본은행 조기 인상 기대. 어드반테스트 +4.0%, 미쓰비시중공업 +4.0%(방위 수주). 신저가 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/13): 항셍 -0.26%·항셍테크 +0.11%로 지수는 눌렸으나 레노버 +16.9%(1분기 순이익 176% 급증·AI서버 수주) 단독 폭등. 헬스테크 순강도 +3(우시앱텍·파마론·스자좡제약).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/13): 상해종합 -0.50%·CSI300 -0.57%. 루이제네트워크 +13.5%(AI 스위치) 외엔 신고가 부재, 유색금속 -3.6%·부동산 -2.4%·태양광 -2.2%로 구경제 일제 약세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①일본은행 인상 기대가 일 은행주에 어디까지 선반영됐는지 ②레노버 실적이 중화권 AI서버 부품·기판 체인으로 번지는지 ③미 금광 7종 신고가가 금값 재상승인지 방어수요인지</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 美는 한국시간 8/13 새벽 마감분. 日·中은 8/13 마감 확정치, 홍콩은 한국시간 16:35 시점 장 마감 30분 전 스냅샷이라 확정치 아님. 텔레그램 적재분은 6/29가 최신이라 시황 참조에서 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +763,19 @@
       <c r="C2" t="n">
         <v>7748.5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>2.72</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>13.19</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +801,19 @@
       <c r="C3" t="n">
         <v>26588.49</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>14.4</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +839,19 @@
       <c r="C4" t="n">
         <v>6813.34</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>3.56</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-13.14</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>61.68</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +877,19 @@
       <c r="C5" t="n">
         <v>68308.59</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>3.03</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>35.7</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +915,19 @@
       <c r="C6" t="n">
         <v>3926.96</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>-0.72</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-5.04</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-1.06</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +953,19 @@
       <c r="C7" t="n">
         <v>4663.95</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.57</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-2.57</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-4.03</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.73</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +991,19 @@
       <c r="C8" t="n">
         <v>25373.97</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.26</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.61</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>2.81</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-3.84</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-1</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1029,19 @@
       <c r="C9" t="n">
         <v>4781.79</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.11</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-6.13</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-13.31</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1160,7 @@
       <c r="F2" t="n">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1201,7 @@
       <c r="F3" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1242,7 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1283,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1324,7 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1365,7 @@
       <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1406,7 @@
       <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1447,7 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1488,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1529,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1570,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1611,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1652,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1693,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1734,7 @@
       <c r="F16" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1775,7 @@
       <c r="F17" t="n">
         <v>-1</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1978,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2019,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2006,7 +2060,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2099,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2086,7 +2140,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2125,7 +2179,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2166,7 +2220,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2205,7 +2259,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2675,7 +2729,7 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2770,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2811,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2796,7 +2850,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2891,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2876,7 +2930,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2917,7 +2971,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3397,7 +3451,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3438,7 +3492,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3479,7 +3533,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -4103,30 +4157,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4147,90 +4202,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4252,58 +4312,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>ETF +1.5%로 11개 섹터 중 최강. 기술서비스 순강도 +8·전자기술 +6, 팔로알토·스노우플레이크·넷앱 신고가.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4323,58 +4388,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.3%. 헬스테크 순강도 +10에 신저가 0, 애보트·메드트로닉·레브비티 신고가. 12MF 19.1배.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4394,58 +4464,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.2%지만 금융 순강도 +11로 전 섹터 최상위. JP모간·BofA·슈왑·US뱅코프 신고가, 12MF 15.2배.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4465,58 +4540,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ETF -1.1%로 약세, 다만 외식만 별도 강세(브링커 +11.1%·다든 +4.0%·텍사스로드하우스 +2.1%). 이베이 신저가.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4536,58 +4616,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ETF -0.9%, 커뮤니케이션 순강도 0으로 신호 없음. YTD -5.8%로 11개 섹터 중 최하위.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4607,58 +4692,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.1% 보합. 산업서비스 +3·생산재 +2, 에머슨·아메텍·무그 신고가. YTD +20.5%로 3위 유지.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4678,58 +4768,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.5%지만 필수소비 순강도 -1(신고1·신저2). 알트리아·데커스 신저가로 내부는 약세.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4749,58 +4844,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.2%·주간 +6.5%로 단기 최강. 정유 주도(마라톤 +3.5%·발레로 +1.9%), 12MF 10.5배로 전 섹터 최저.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>38.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4820,58 +4920,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.5%, 셰니에르에너지파트너스 +3.4% 신고가. 1M -4.0%로 중기 부진은 지속.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4891,58 +4996,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ETF -1.2%로 당일 최약. 비에너지소재 순강도 +9는 금광 7종(뉴몬트·애그니코 등)이 만든 값으로 화학 중심 XLB와 괴리.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4962,58 +5072,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.9%로 반등했으나 주간 -1.6%. W.P.캐리 신저가 잔존으로 내부 온도차 존재.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5033,58 +5148,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5104,58 +5220,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5175,58 +5292,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5246,58 +5364,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5317,58 +5436,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5388,58 +5508,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5459,58 +5580,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>53.8</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5530,58 +5652,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5601,58 +5724,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>39.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5672,58 +5796,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5743,58 +5868,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5814,58 +5940,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5885,58 +6012,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5956,58 +6084,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6027,58 +6156,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6098,58 +6228,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6169,58 +6300,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6240,58 +6372,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6311,58 +6444,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6382,56 +6516,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-12.9</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6449,58 +6584,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>ETF -1.7% 조정, 다만 YTD +46.2%로 13개 중 1위. 진왕전자 장중 신고가 후 차익실현 마감.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-13.1</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6520,58 +6660,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>ETF -0.9%지만 루이제네트워크 +13.5% 신고가 — AI연산 관련만 선별 강세.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6591,58 +6736,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.2%로 A주에서 드문 상승, 주간 +3.6%. 네트워크장비 강세와 방향 일치.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-12.4</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6662,56 +6812,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>ETF -1.1%, 3개월 -18.4%로 부진 지속. 홍콩 니오 신저가와 동조.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-18.4</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6729,58 +6884,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>ETF -0.7%, 3개월 -17.1%. 일본 미쓰비시중공업 방산 신고가와는 대조적 약세.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16.4</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6800,56 +6960,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>ETF -2.2%로 당일 하위권, 3개월 -22.1%로 13개 중 최악. 신고가 종목 없음.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-10.3</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6867,58 +7032,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.9%로 당일 A주 최강, 1M +8.2%. 소비 회복 기대 선반영 추정.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-16</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6938,58 +7108,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>ETF 보합(0.0%). 미·일 은행이 동반 신고가를 낸 것과 달리 A주 금융 순강도는 0으로 무반응.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7009,58 +7184,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>ETF -3.6%로 당일 최약. 미 금광 7종 신고가와 정반대 — 귀금속 아닌 산업금속 비중 탓으로 추정.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7080,58 +7260,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>ETF -2.4%, YTD -17.3%로 13개 중 최하위. 홍콩 중국철도건설 신저가와 동조.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7151,58 +7336,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>ETF +0.4%로 지수(-0.5%) 대비 선방. 다만 신고가 종목은 없음.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.1</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7222,58 +7412,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>ETF -0.2%지만 파마론 +4.0% 신고가, 주간 +5.5%·3M +12.4%로 A주 내 상위권.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7293,58 +7488,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ETF -0.4%, YTD -14.2%. 백주만 오르고 광의 소비는 약세로 갈리는 구도.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7356,7 +7556,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3.6"/>
@@ -7368,7 +7568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.5"/>
@@ -7380,7 +7580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-13.1"/>
@@ -7392,7 +7592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.1"/>
@@ -7404,7 +7604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-17.3"/>
@@ -7416,7 +7616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7428,7 +7628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7440,7 +7640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7452,7 +7652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7464,7 +7664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7476,7 +7676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7590,7 +7790,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7643,10 +7843,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7699,10 +7899,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7755,14 +7955,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 팔로알토네트웍스(기업 보안SW): 오펜하이머·바클레이스 목표가 상향+AI에이전트 해킹 보도로 보안주 랠리</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7811,15 +8011,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7867,10 +8067,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7919,10 +8119,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7971,10 +8171,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8027,10 +8227,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8079,15 +8279,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8131,15 +8331,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8183,10 +8383,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8235,15 +8435,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8289,10 +8489,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8339,14 +8539,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 알트리아(미국 담배): 7월말 2분기 부진·가이던스 하향 여파 지속, 고배당주 소외</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8399,15 +8599,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8455,10 +8655,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8507,10 +8707,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8563,10 +8763,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8619,15 +8819,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8671,15 +8871,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8727,10 +8927,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8783,10 +8983,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8835,10 +9035,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8891,15 +9091,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8939,15 +9139,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8991,15 +9191,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9047,10 +9247,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9099,15 +9299,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9151,15 +9351,15 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9203,10 +9403,14 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>이베이(온라인 중고·경매 커머스 플랫폼): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9259,15 +9463,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9315,10 +9519,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9363,14 +9567,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9419,10 +9623,10 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9475,14 +9679,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) 에버퓨어(올플래시 데이터 스토리지): 서스퀘하나 투자의견 상향, AI·클라우드 플래시 수요 부각</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9529,10 +9733,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9585,10 +9789,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9637,15 +9841,15 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9687,15 +9891,15 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9743,10 +9947,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9795,10 +9999,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9851,10 +10055,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9907,15 +10111,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>다든레스토랑츠(올리브가든 등 외식체인): 신규 촉매 미확인(브링커 서프라이즈발 외식섹터 동반강세 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9959,15 +10167,15 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10011,10 +10219,10 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10067,15 +10275,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10119,15 +10327,19 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>텍사스퍼시픽랜드(퍼미안분지 토지·로열티): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10175,10 +10387,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10225,15 +10437,15 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10281,15 +10493,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>테넷헬스케어(병원·외래수술센터 운영): BofA·미즈호 등 목표가 상향에 52주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10329,15 +10545,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10385,15 +10601,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10437,10 +10653,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10489,15 +10705,15 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10539,10 +10755,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10591,10 +10807,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10643,10 +10859,10 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10699,10 +10915,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10755,19 +10971,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="7" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>(전일) 제임스하디(파이버시멘트 건축자재): FY27 1분기 EBITDA 가이던스 상회, AZEK 통합 기대</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10815,10 +11031,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>롤린스(해충방제 서비스): 특별한 뉴스 없음(7월 실적 EPS 미스 여진 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10867,10 +11087,10 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10923,10 +11143,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10975,15 +11195,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11031,10 +11251,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11083,15 +11303,15 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11139,10 +11359,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11195,19 +11415,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>(전일) 바이오마린(희귀질환 바이오제약): 8/6 2분기 EPS 서프라이즈·가이던스 상향 여진</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11255,10 +11475,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>무그(항공우주·방산용 정밀 모션제어 부품): 특별한 뉴스 없음(방산 섹터 강세 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11309,15 +11533,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11361,15 +11585,15 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11409,15 +11633,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11461,15 +11685,19 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>워너뮤직그룹(글로벌 3대 음반사): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11513,15 +11741,19 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>데커스아웃도어(어그·호카 신발 브랜드): 잭스리서치 실적추정치 하향 보고서로 하락</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11565,10 +11797,10 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11615,10 +11847,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11667,15 +11899,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11721,15 +11953,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>글라우코스(안과 의료기기·녹내장 치료제): 2분기 매출 서프라이즈·2026년 매출 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11773,15 +12009,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>프락시스프리시전메디슨(중추신경계 질환 신약 개발 바이오텍): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11829,15 +12069,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11883,10 +12123,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>브링커인터내셔널(칠리스 등 캐주얼다이닝 체인): FY26 4분기 실적 서프라이즈·FY27 가이던스 상회</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11935,7 +12179,7 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N82"/>
@@ -12041,7 +12285,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12088,15 +12332,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12144,10 +12388,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>어드반테스트(반도체 검사장비): AI 테스터 수요 급증에 분기 실적 사상 최대·반도체주 회복</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12200,19 +12448,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12254,15 +12502,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시중공업(중공업·방위산업): 방위비 확대·수주잔고 급증으로 1분기 이익 급증</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12310,15 +12562,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>리소나홀딩스(소매 특화 은행 지주): 일본은행 조기 금리인상 기대에 은행주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12366,10 +12622,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>스미토모미쓰이트러스트그룹(신탁은행 지주): 금리상승 기대와 1분기 실적 호조로 강세</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12416,14 +12676,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12470,14 +12730,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12526,15 +12786,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12582,15 +12842,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>치바은행(지방은행): 일본은행 조기 금리인상 기대에 은행주 동반 강세·신고가</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12638,15 +12902,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12688,10 +12952,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12744,7 +13008,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N14"/>
@@ -12850,7 +13114,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12901,14 +13165,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12961,19 +13225,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>레노버(피시·서버 세계 1위): 26/27 회계 1분기 순이익 176% 급증, 인공지능 서버 수주 급증</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13017,15 +13281,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>차오저우싼환(적층세라믹콘덴서 등 전자부품): 고용량 부품 가격 인상·반도체 업종 반등에 수급 개선</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13071,15 +13339,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>중전홀딩스(홍콩 전력 공급): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13119,10 +13391,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>갤럭시엔터테인먼트(마카오 카지노 운영): 7월 마카오 카지노 매출 점유율 1위로 회복 기대</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13173,15 +13449,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13225,15 +13501,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>스자좡제약그룹(제약): 상반기 순이익 서프라이즈 가이던스, 신약 임상 진전 겹호재</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13279,10 +13559,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>중국철도건설(인프라·건설 국유기업): 특별한 뉴스 없음(건설·인프라 섹터 약세 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13335,19 +13619,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 캉룽화청(신약 위탁연구 CRO): CXO 섹터 랠리 지속·실적 호조로 목표주가 상향 잇따름(개별 신규 촉매는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13387,7 +13671,11 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>니오(중국 전기차): 특별한 뉴스 없음(전기차 업종 약세 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N11"/>
@@ -13493,12 +13781,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13546,15 +13834,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>루이제네트워크(데이터센터·기업용 스위치): 인공지능 연산 인프라 수요로 클라우드사향 공급 확대 기대</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13600,10 +13892,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>진왕전자(인쇄회로기판 제조): 홍콩 상장 추진 호재로 급등 후, 이상급등 경보에 차익실현 매물로 소폭 하락</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13656,7 +13952,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
         </is>

--- a/신고신저가_20260813.xlsx
+++ b/신고신저가_20260813.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25373.97</v>
+        <v>25396.51</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-0.26</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.61</v>
+        <v>-0.52</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-3.84</v>
+        <v>-3.76</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-1</v>
+        <v>-0.91</v>
       </c>
       <c r="I8" t="n">
         <v>51</v>
@@ -1027,22 +1027,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4781.79</v>
+        <v>4792.39</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.59</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.87</v>
+        <v>1.09</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-6.13</v>
+        <v>-5.92</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-13.31</v>
+        <v>-13.12</v>
       </c>
       <c r="I9" t="n">
         <v>22</v>
@@ -1295,10 +1295,10 @@
         <v>87</v>
       </c>
       <c r="J5" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6">
@@ -1785,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>187.2</v>
+        <v>184.6</v>
       </c>
       <c r="K17" t="n">
         <v>7.9</v>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="I42" t="n">
         <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="K42" t="n">
         <v>5.8</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="I44" t="n">
         <v>5</v>
@@ -2865,7 +2865,7 @@
         <v>15.7</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="45">
@@ -3020,7 +3020,7 @@
         <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="K48" t="n">
         <v>4.3</v>
@@ -3101,7 +3101,7 @@
         <v>12.1</v>
       </c>
       <c r="K50" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="51">
@@ -3175,7 +3175,7 @@
         <v>10.8</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
         <v>7.8</v>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="I55" t="n">
         <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="K55" t="n">
         <v>2.8</v>
@@ -3333,14 +3333,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="K56" t="n">
         <v>1.7</v>
@@ -3375,13 +3373,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="I57" t="n">
         <v>6</v>
       </c>
       <c r="J57" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="K57" t="n">
         <v>3.2</v>
@@ -3416,7 +3414,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="I58" t="n">
         <v>7</v>
@@ -3979,7 +3977,7 @@
         <v>27</v>
       </c>
       <c r="K72" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -6446,13 +6444,13 @@
       </c>
       <c r="D31" s="8" t="inlineStr"/>
       <c r="E31" s="9" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H31" s="9" t="n">
         <v>-4.7</v>
@@ -6518,19 +6516,19 @@
       </c>
       <c r="D32" s="8" t="inlineStr"/>
       <c r="E32" s="9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>-12.9</v>
+        <v>-12.7</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -9403,11 +9401,7 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>이베이(온라인 중고·경매 커머스 플랫폼): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10111,11 +10105,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>다든레스토랑츠(올리브가든 등 외식체인): 신규 촉매 미확인(브링커 서프라이즈발 외식섹터 동반강세 추정)</t>
-        </is>
-      </c>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10327,11 +10317,7 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>텍사스퍼시픽랜드(퍼미안분지 토지·로열티): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10493,11 +10479,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr">
-        <is>
-          <t>테넷헬스케어(병원·외래수술센터 운영): BofA·미즈호 등 목표가 상향에 52주 신고가</t>
-        </is>
-      </c>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -11031,11 +11013,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr">
-        <is>
-          <t>롤린스(해충방제 서비스): 특별한 뉴스 없음(7월 실적 EPS 미스 여진 추정)</t>
-        </is>
-      </c>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -11475,11 +11453,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
-        <is>
-          <t>무그(항공우주·방산용 정밀 모션제어 부품): 특별한 뉴스 없음(방산 섹터 강세 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -11685,11 +11659,7 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="10" t="inlineStr">
-        <is>
-          <t>워너뮤직그룹(글로벌 3대 음반사): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -11741,11 +11711,7 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>데커스아웃도어(어그·호카 신발 브랜드): 잭스리서치 실적추정치 하향 보고서로 하락</t>
-        </is>
-      </c>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11953,11 +11919,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="10" t="inlineStr">
-        <is>
-          <t>글라우코스(안과 의료기기·녹내장 치료제): 2분기 매출 서프라이즈·2026년 매출 가이던스 상향</t>
-        </is>
-      </c>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -12009,11 +11971,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
-        <is>
-          <t>프락시스프리시전메디슨(중추신경계 질환 신약 개발 바이오텍): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -12123,11 +12081,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
-        <is>
-          <t>브링커인터내셔널(칠리스 등 캐주얼다이닝 체인): FY26 4분기 실적 서프라이즈·FY27 가이던스 상회</t>
-        </is>
-      </c>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -12388,11 +12342,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>어드반테스트(반도체 검사장비): AI 테스터 수요 급증에 분기 실적 사상 최대·반도체주 회복</t>
-        </is>
-      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -12502,11 +12452,7 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>미쓰비시중공업(중공업·방위산업): 방위비 확대·수주잔고 급증으로 1분기 이익 급증</t>
-        </is>
-      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -12562,11 +12508,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>리소나홀딩스(소매 특화 은행 지주): 일본은행 조기 금리인상 기대에 은행주 동반 강세</t>
-        </is>
-      </c>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -12622,11 +12564,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>스미토모미쓰이트러스트그룹(신탁은행 지주): 금리상승 기대와 1분기 실적 호조로 강세</t>
-        </is>
-      </c>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -12842,11 +12780,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>치바은행(지방은행): 일본은행 조기 금리인상 기대에 은행주 동반 강세·신고가</t>
-        </is>
-      </c>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13140,10 +13074,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>203.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
         <v>69.7</v>
@@ -13152,7 +13086,7 @@
         <v>23.9</v>
       </c>
       <c r="J2" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
@@ -13198,22 +13132,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>33.96</v>
+        <v>34.9</v>
       </c>
       <c r="G3" t="n">
-        <v>16.94</v>
+        <v>20.18</v>
       </c>
       <c r="H3" t="n">
         <v>45.9</v>
       </c>
       <c r="I3" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="J3" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -13227,7 +13161,7 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>레노버(피시·서버 세계 1위): 26/27 회계 1분기 순이익 176% 급증, 인공지능 서버 수주 급증</t>
+          <t>(전일) 레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
         </is>
       </c>
     </row>
@@ -13258,10 +13192,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>129.6</v>
+        <v>130.8</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
         <v>37.4</v>
@@ -13269,7 +13203,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -13281,11 +13215,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>차오저우싼환(적층세라믹콘덴서 등 전자부품): 고용량 부품 가격 인상·반도체 업종 반등에 수급 개선</t>
-        </is>
-      </c>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -13314,10 +13244,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>78.5</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="H5" t="n">
         <v>25.1</v>
@@ -13339,11 +13269,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>중전홀딩스(홍콩 전력 공급): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -13372,10 +13298,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34.88</v>
+        <v>34.94</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
         <v>19.1</v>
@@ -13391,11 +13317,7 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>갤럭시엔터테인먼트(마카오 카지노 운영): 7월 마카오 카지노 매출 점유율 1위로 회복 기대</t>
-        </is>
-      </c>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -13424,17 +13346,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103.7</v>
+        <v>103.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
         <v>15.8</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
         <v>0.5</v>
@@ -13478,22 +13400,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8.869999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
         <v>12.7</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -13501,11 +13423,7 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>스자좡제약그룹(제약): 상반기 순이익 서프라이즈 가이던스, 신약 임상 진전 겹호재</t>
-        </is>
-      </c>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -13534,10 +13452,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.88</v>
+        <v>-1.2</v>
       </c>
       <c r="H9" t="n">
         <v>11.6</v>
@@ -13559,11 +13477,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>중국철도건설(인프라·건설 국유기업): 특별한 뉴스 없음(건설·인프라 섹터 약세 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -13592,19 +13506,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30.26</v>
+        <v>30.4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.34</v>
+        <v>4.83</v>
       </c>
       <c r="H10" t="n">
         <v>11.6</v>
       </c>
       <c r="I10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="J10" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -13652,10 +13566,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>35.22</v>
+        <v>35.32</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.29</v>
+        <v>-1.01</v>
       </c>
       <c r="H11" t="n">
         <v>10.6</v>
@@ -13663,7 +13577,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -13671,11 +13585,7 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>니오(중국 전기차): 특별한 뉴스 없음(전기차 업종 약세 흐름 추정)</t>
-        </is>
-      </c>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N11"/>
@@ -13813,7 +13723,7 @@
         <v>13.52</v>
       </c>
       <c r="H2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="I2" t="n">
         <v>94.3</v>
@@ -13834,11 +13744,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>루이제네트워크(데이터센터·기업용 스위치): 인공지능 연산 인프라 수요로 클라우드사향 공급 확대 기대</t>
-        </is>
-      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -13892,11 +13798,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>진왕전자(인쇄회로기판 제조): 홍콩 상장 추진 호재로 급등 후, 이상급등 경보에 차익실현 매물로 소폭 하락</t>
-        </is>
-      </c>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">

--- a/신고신저가_20260813.xlsx
+++ b/신고신저가_20260813.xlsx
@@ -618,49 +618,49 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 지수는 미·일만 전진하고 중화권은 정체 — 그 안에서 금융(미·일)과 AI 하드웨어(레노버·어드반테스트·루이제)만 신고가를 만드는 좁고 선별적인 장세로 판단.</t>
+          <t>💬 ■ 결론: 신고가를 만드는 축은 AI 하드웨어(레노버·어드반테스트·루이제·차오저우싼환)와 금융(미 은행·일 은행) 둘뿐 — 지수는 미·일만 전진하고 중화권 구경제는 밀리는 좁고 선별적 장세로 판단.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 美(8/12): S&amp;P500 +0.26%(7,748·52주위치 99%)·나스닥 +0.54%, 신고70/신저11. 금융 순강도 +11(12MF 15.2배)·헬스테크 +10·비에너지소재 +9. 뉴몬트·애그니코 등 금광 7종 동반 신고가. XLK +1.5% 대 XLB -1.2%·XLY -1.1%. 브링커 +11.1%(FY26 4분기 서프라이즈), 텍사스퍼시픽랜드 -6.1%.</t>
+          <t>■ 美(8/12): S&amp;P500 +0.26%(7,748·52주위치 99%)·나스닥 +0.54%, 신고70(NEW32)/신저11(NEW5). 금융 순강도 +11(12MF 15.2배·표본161)·헬스테크 +10(19.1배)·비에너지소재 +9(15.8배). 뉴몬트·애그니코·웨스턴프레셔스 등 금광 7종 동반 신고가. XLK +1.5% 대 XLB -1.2%·XLY -1.1%·XLC -0.9%. 브링커 +11.1%(FY26 4분기 서프라이즈·FY27 가이던스 상회), 텍사스퍼시픽랜드 -6.1%, 이베이 -3.5%(게임스톱 인수 철회설로 프리미엄 되돌림).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 日(8/13): 닛케이 +1.16%(68,309). 은행ETF +3.0%로 최강, 리소나 +4.4%·치바은행 +3.5%·스미토모미쓰이트러스트 +2.8% 일제 신고가 — 일본은행 조기 인상 기대. 어드반테스트 +4.0%, 미쓰비시중공업 +4.0%(방위 수주). 신저가 0.</t>
+          <t>■ 日(8/13): 닛케이 +1.16%(68,309), 신고13(NEW7)·신저 0. 은행ETF +3.0%로 업종 최강 — 리소나 +4.4%·지바은행 +3.5%·스미토모미쓰이트러스트 +2.8%·시즈오카 +2.3% 일제 신고가, 정부의 조기 금리인상 지지 보도가 촉매. 어드반테스트 +4.0%(AI 테스터 수요), 미쓰비시중공업 +4.0%(방위비 증액 기대). 전기·정밀 +2.2%·기계 +2.0%.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 홍콩(8/13): 항셍 -0.26%·항셍테크 +0.11%로 지수는 눌렸으나 레노버 +16.9%(1분기 순이익 176% 급증·AI서버 수주) 단독 폭등. 헬스테크 순강도 +3(우시앱텍·파마론·스자좡제약).</t>
+          <t>■ 홍콩(8/13): 항셍 -0.17%·항셍테크 +0.33%로 지수는 눌렸으나 레노버 +20.2% 단독 폭등(FY26/27 1분기 매출 +43%·조정순이익 +176%, AI서버 매출 사상 최고). 차오저우싼환 +9.0%(AI용 고급 MLCC 공급부족). 헬스테크 순강도 +3(우시앱텍·파마론·스야오그룹). 신저는 중국철도건설·니오 2종.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 中(8/13): 상해종합 -0.50%·CSI300 -0.57%. 루이제네트워크 +13.5%(AI 스위치) 외엔 신고가 부재, 유색금속 -3.6%·부동산 -2.4%·태양광 -2.2%로 구경제 일제 약세.</t>
+          <t>■ 中(8/13): 상해종합 -0.50%(3,927)·CSI300 -0.57%, 신고 3종뿐·신저 0. 루이제네트워크 +13.5%(AI 스위치 국산화) 외엔 신고가 부재. 유색금속 -3.6%·부동산 -2.4%·태양광 -2.2%·반도체 -1.7%로 구경제·성장 동반 약세, 백주 +0.9%만 방어.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①일본은행 인상 기대가 일 은행주에 어디까지 선반영됐는지 ②레노버 실적이 중화권 AI서버 부품·기판 체인으로 번지는지 ③미 금광 7종 신고가가 금값 재상승인지 방어수요인지</t>
+          <t>■ 체크: ①일본은행 조기 인상 기대가 일 은행주에 어디까지 선반영됐는지(은행ETF YTD26 +24.1%) ②레노버 실적이 중화권 AI서버 부품·PCB·MLCC 체인으로 번지는지(진왕전자·차오저우싼환) ③미 금광 7종 신고가가 금값 재상승인지 방어수요인지 ④중국A 반도체ETF -1.7%인데 루이제만 급등한 괴리</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ 참고: 美는 한국시간 8/13 새벽 마감분. 日·中은 8/13 마감 확정치, 홍콩은 한국시간 16:35 시점 장 마감 30분 전 스냅샷이라 확정치 아님. 텔레그램 적재분은 6/29가 최신이라 시황 참조에서 제외.</t>
+          <t>■ 참고: 이번 실행은 8/13 저녁 19시(KST) 기준. 美는 8/12 마감분이고 8/13 미장은 아직 개장 전(22:30 KST). 日·홍콩·中A는 모두 8/13 마감 확정치(오전 16:51 실행분의 홍콩 장중 스냅샷을 마감가로 교체 — 레노버 +16.9%→+20.2%). 텔레그램 적재분은 6/29가 최신이라 시황 참조에서 제외.</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>ETF +1.5%로 11개 섹터 중 최강. 기술서비스 순강도 +8·전자기술 +6, 팔로알토·스노우플레이크·넷앱 신고가.</t>
+          <t>1D +1.5%로 미 섹터 최강. 전자기술 순강도 +6·테크서비스 +8, 넷앱·유니티·스노우플레이크 신고가</t>
         </is>
       </c>
       <c r="E2" s="9" t="n">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.3%. 헬스테크 순강도 +10에 신저가 0, 애보트·메드트로닉·레브비티 신고가. 12MF 19.1배.</t>
+          <t>1D +0.3%, 3M +16.0%로 중기 1위권. 헬스테크 순강도 +10(12MF 19.1배), 테넷·글라우코스·프락시스 신고가</t>
         </is>
       </c>
       <c r="E3" s="9" t="n">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.2%지만 금융 순강도 +11로 전 섹터 최상위. JP모간·BofA·슈왑·US뱅코프 신고가, 12MF 15.2배.</t>
+          <t>1D +0.2%지만 금융 순강도 +11로 종목 폭은 최강. 12MF 15.2배(표본161), JP모건·BoA·슈왑·US뱅코프 신고가</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>ETF -1.1%로 약세, 다만 외식만 별도 강세(브링커 +11.1%·다든 +4.0%·텍사스로드하우스 +2.1%). 이베이 신저가.</t>
+          <t>1D -1.1%로 약세. 다만 외식(브링커 +11.1%·텍사스로드하우스·다든)만 별도로 신고가 형성</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>ETF -0.9%, 커뮤니케이션 순강도 0으로 신호 없음. YTD -5.8%로 11개 섹터 중 최하위.</t>
+          <t>1D -0.9%, 3M -4.6%로 미 섹터 최약. 워너뮤직 신저가, 워너브러더스디스커버리만 신고가로 갈림</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.1% 보합. 산업서비스 +3·생산재 +2, 에머슨·아메텍·무그 신고가. YTD +20.5%로 3위 유지.</t>
+          <t>1D +0.1% 보합. 산업서비스 순강도 +3·생산재 +2, 무그·아메텍·록히드마틴 신고가로 방산 축이 견인</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.5%지만 필수소비 순강도 -1(신고1·신저2). 알트리아·데커스 신저가로 내부는 약세.</t>
+          <t>1D +0.5%로 방어 강세. 다만 필수소비재 순강도 -1(알트리아·데커스 신저가)로 종목 폭은 약함</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.2%·주간 +6.5%로 단기 최강. 정유 주도(마라톤 +3.5%·발레로 +1.9%), 12MF 10.5배로 전 섹터 최저.</t>
+          <t>1D +0.2%·1주 +6.5%로 주간 최강. 에너지 순강도 +4(12MF 10.5배 최저), 마라톤·발레로 등 정유 신고가</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.5%, 셰니에르에너지파트너스 +3.4% 신고가. 1M -4.0%로 중기 부진은 지속.</t>
+          <t>1D +0.5%지만 1M -4.0%로 중기 부진. 유틸리티 순강도 +1(셰니어에너지파트너스 +3.4%)</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>ETF -1.2%로 당일 최약. 비에너지소재 순강도 +9는 금광 7종(뉴몬트·애그니코 등)이 만든 값으로 화학 중심 XLB와 괴리.</t>
+          <t>1D -1.2%로 최약이나 비에너지소재 순강도 +9 — 화학 약세 대 금광(뉴몬트·애그니코 등 7종) 신고가로 양분</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.9%로 반등했으나 주간 -1.6%. W.P.캐리 신저가 잔존으로 내부 온도차 존재.</t>
+          <t>1D +0.9%로 반등했으나 1주 -1.6%. 리츠 신고가 부재, W.P.케리는 신저가권 잔류</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>ETF -1.7% 조정, 다만 YTD +46.2%로 13개 중 1위. 진왕전자 장중 신고가 후 차익실현 마감.</t>
+          <t>1D -1.7%·1M -13.1%로 조정 지속. 반도체 신고가 0종, 진왕전자만 장중 신고가 터치 후 -1.0% 마감</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>ETF -0.9%지만 루이제네트워크 +13.5% 신고가 — AI연산 관련만 선별 강세.</t>
+          <t>1D -0.9%·1M -10.0%. 다만 루이제네트워크 +13.5%(AI 스위치)로 AI 네트워크만 별도 강세</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.2%로 A주에서 드문 상승, 주간 +3.6%. 네트워크장비 강세와 방향 일치.</t>
+          <t>1D +0.2%로 유일한 통신 강보합. 1M -12.4%로 중기 낙폭은 여전히 큼(추정: 낙폭과대 반등)</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>ETF -1.1%, 3개월 -18.4%로 부진 지속. 홍콩 니오 신저가와 동조.</t>
+          <t>1D -1.1%·3M -18.4%로 최약권. 홍콩 상장 니오 신저가와 방향 일치, 전기차 수급 약세</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>ETF -0.7%, 3개월 -17.1%. 일본 미쓰비시중공업 방산 신고가와는 대조적 약세.</t>
+          <t>1D -0.7%·3M -17.1%. 방산 신고가 부재, 일본 방산(미쓰비시중공업 +4.0%)과 대조적 부진</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>ETF -2.2%로 당일 하위권, 3개월 -22.1%로 13개 중 최악. 신고가 종목 없음.</t>
+          <t>1D -2.2%·3M -22.1%로 3개월 최약. 태양광 신고가 0종, 과잉공급 부담 지속(추정)</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.9%로 당일 A주 최강, 1M +8.2%. 소비 회복 기대 선반영 추정.</t>
+          <t>1D +0.9%·1M +8.2%로 중국A 유일 강세. 지수 하락일의 방어·내수 선호 흐름(추정)</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>ETF 보합(0.0%). 미·일 은행이 동반 신고가를 낸 것과 달리 A주 금융 순강도는 0으로 무반응.</t>
+          <t>1D 0.0% 보합. 금융 순강도 0, 12MF 7.3배(표본10)로 밸류는 최저권이나 촉매 부재</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>ETF -3.6%로 당일 최약. 미 금광 7종 신고가와 정반대 — 귀금속 아닌 산업금속 비중 탓으로 추정.</t>
+          <t>1D -3.6%로 당일 최대 낙폭. 1M +7.5%였던 급등분 되돌림, 미 금광 신고가와 정반대 움직임</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>ETF -2.4%, YTD -17.3%로 13개 중 최하위. 홍콩 중국철도건설 신저가와 동조.</t>
+          <t>1D -2.4%·3M -13.5%. 부동산 신고가 0종, 홍콩 중국철도건설 신저가와 인프라·부동산 동반 약세</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>ETF +0.4%로 지수(-0.5%) 대비 선방. 다만 신고가 종목은 없음.</t>
+          <t>1D +0.4%로 소폭 강세. 증권 신고가 부재, 거래대금 기대 선반영 여부는 미확인</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>ETF -0.2%지만 파마론 +4.0% 신고가, 주간 +5.5%·3M +12.4%로 A주 내 상위권.</t>
+          <t>1D -0.2%지만 1주 +5.5%·3M +12.4%로 중기 상위. 파마론 A주 +4.0% 신고가, CRO 축이 견인</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>ETF -0.4%, YTD -14.2%. 백주만 오르고 광의 소비는 약세로 갈리는 구도.</t>
+          <t>1D -0.4%·1M +3.7%. 소비 신고가 부재, 백주(+0.9%)만 갈라져 강세</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
@@ -9401,7 +9401,11 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>이베이(온라인 중고·경매 커머스): 게임스톱의 566억달러 인수 철회·제휴 선회설로 인수 프리미엄 되돌림 지속</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10105,7 +10109,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>다든레스토랑츠(올리브가든 등 외식체인): 연속 강세 지속(신규 촉매 미확인, 외식업종 동반 강세 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10317,7 +10325,11 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>텍사스퍼시픽랜드(퍼미안분지 토지·로열티 보유): 특별한 뉴스 없음(에너지 섹터 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10479,7 +10491,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>테넷헬스케어(병원·외래수술센터 운영): 2분기 서프라이즈·가이던스 상향 여파로 강세 지속, 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -11013,7 +11029,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr">
+        <is>
+          <t>롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -11453,7 +11473,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>무그(항공우주·방산 정밀제어시스템): 3분기 실적 호조·FY26 매출 가이던스 44억달러로 상향</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -11659,7 +11683,11 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="10" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>워너뮤직그룹(3대 메이저 음반사): 특별한 뉴스 없음(8/5 실적 후 마진 논쟁 속 약세 지속 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -11711,7 +11739,11 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="10" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>데커스아웃도어(호카·어그 브랜드 신발): 특별한 뉴스 없음(성장 둔화 우려 속 차익실현 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11919,7 +11951,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="10" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>글라우코스(녹내장·각막질환 의료기기): 2분기 매출 급증·2026년 가이던스 상향, 목표주가 잇단 상향</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -11971,7 +12007,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>프락시스정밀의학(신경질환 치료제 바이오텍): RBC·베어드 목표주가 상향, 2분기 실적 호조 지속</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -12081,7 +12121,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>브링커인터내셔널(칠리스 등 캐주얼다이닝 체인): 4분기 매출 서프라이즈·FY27 가이던스 상회로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -12342,7 +12386,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>어드반테스트(반도체 테스터 장비): AI 반도체 테스터 수요 급증·실적 상향으로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -12452,7 +12500,11 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -12508,7 +12560,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -12564,7 +12620,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -12780,7 +12840,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13161,7 +13225,7 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>(전일) 레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
+          <t>레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13279,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -13269,7 +13337,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -13317,7 +13389,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>갤럭시엔터테인먼트(마카오 카지노·리조트): 8월 마카오 카지노 매출 호조 전망에 외국계 매수의견 강화</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -13423,7 +13499,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>스야오그룹(CSPC, 항생제·비타민C·혁신신약 제약사): 특별한 뉴스 없음(8/20 중간실적 앞둔 제약 수급 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -13477,7 +13557,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -13585,7 +13669,11 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>니오(중국 프리미엄 전기차): 특별한 뉴스 없음(전기차 섹터 수급 약세 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N11"/>
@@ -13744,7 +13832,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>루이제네트워크(데이터센터 스위치·네트워크장비): AI연산 수요 급증에 국산화 대체 기대로 상한가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -13798,7 +13890,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>진왕전자(PCB 제조): AI서버·광모듈용 PCB 수요로 연일 급등 후 차익실현 매물, 신고가는 장중 터치</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
